--- a/artfynd/A 47697-2025 artfynd.xlsx
+++ b/artfynd/A 47697-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130019017</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>130013311</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>130013040</v>
       </c>
       <c r="B4" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>130019441</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>130013086</v>
       </c>
       <c r="B7" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>130013291</v>
       </c>
       <c r="B8" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>130021276</v>
       </c>
       <c r="B9" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>130019442</v>
       </c>
       <c r="B10" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47697-2025 artfynd.xlsx
+++ b/artfynd/A 47697-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130019017</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>130013311</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>130013040</v>
       </c>
       <c r="B4" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>130019441</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>130013086</v>
       </c>
       <c r="B7" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>130013291</v>
       </c>
       <c r="B8" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>130021276</v>
       </c>
       <c r="B9" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>130019442</v>
       </c>
       <c r="B10" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47697-2025 artfynd.xlsx
+++ b/artfynd/A 47697-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130019017</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>130013311</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>130013040</v>
       </c>
       <c r="B4" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>130019441</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>130013086</v>
       </c>
       <c r="B7" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>130013291</v>
       </c>
       <c r="B8" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>130021276</v>
       </c>
       <c r="B9" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>130019442</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47697-2025 artfynd.xlsx
+++ b/artfynd/A 47697-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130019017</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>130013311</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>130013040</v>
       </c>
       <c r="B4" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>130019441</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>130013086</v>
       </c>
       <c r="B7" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>130013291</v>
       </c>
       <c r="B8" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>130021276</v>
       </c>
       <c r="B9" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>130019442</v>
       </c>
       <c r="B10" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47697-2025 artfynd.xlsx
+++ b/artfynd/A 47697-2025 artfynd.xlsx
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130013040</v>
+        <v>130021271</v>
       </c>
       <c r="B4" t="n">
-        <v>93010</v>
+        <v>5177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,46 +922,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Laggarboberget, Laggarboberget, Dlr</t>
+          <t>Laggarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525214</v>
+        <v>525359</v>
       </c>
       <c r="R4" t="n">
-        <v>6692941</v>
+        <v>6693206</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,28 +1009,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130021271</v>
+        <v>130013040</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>93010</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,46 +1039,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Laggarboberget, Dlr</t>
+          <t>Laggarboberget, Laggarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525359</v>
+        <v>525214</v>
       </c>
       <c r="R5" t="n">
-        <v>6693206</v>
+        <v>6692941</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1117,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,19 +1126,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 47697-2025 artfynd.xlsx
+++ b/artfynd/A 47697-2025 artfynd.xlsx
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130021271</v>
+        <v>130013040</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>93010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,46 +922,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Laggarboberget, Dlr</t>
+          <t>Laggarboberget, Laggarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525359</v>
+        <v>525214</v>
       </c>
       <c r="R4" t="n">
-        <v>6693206</v>
+        <v>6692941</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,29 +1009,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130013040</v>
+        <v>130021271</v>
       </c>
       <c r="B5" t="n">
-        <v>93010</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,46 +1038,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Laggarboberget, Laggarboberget, Dlr</t>
+          <t>Laggarboberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525214</v>
+        <v>525359</v>
       </c>
       <c r="R5" t="n">
-        <v>6692941</v>
+        <v>6693206</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,18 +1125,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
